--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_294_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_294_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0388</v>
+        <v>8.1586</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3173</v>
+        <v>6.5715</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7216</v>
+        <v>1.5871</v>
       </c>
       <c r="G2" t="n">
         <v>4.4713</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7187</v>
+        <v>0.4011</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2696</v>
+        <v>-0.0154</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.4165</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1487</v>
+        <v>4.9305</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2155</v>
+        <v>2.762</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9332</v>
+        <v>2.1685</v>
       </c>
       <c r="G3" t="n">
         <v>2.7955</v>
@@ -688,13 +688,13 @@
         <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.358</v>
+        <v>0.4237</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3339</v>
+        <v>0.2126</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0242</v>
+        <v>0.2111</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0062</v>
+        <v>3.6697</v>
       </c>
       <c r="E4" t="n">
-        <v>3.198</v>
+        <v>1.1882</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8082</v>
+        <v>2.4814</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5831</v>
+        <v>2.5948</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6218</v>
+        <v>0.3998</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2049</v>
+        <v>2.195</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1017</v>
+        <v>1.369</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1043</v>
+        <v>0.1176</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9974</v>
+        <v>1.2514</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5185999999999999</v>
+        <v>1.2258</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7261</v>
+        <v>0.2822</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2075</v>
+        <v>0.9436</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1215</v>
+        <v>-0.1751</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1142</v>
+        <v>-0.1808</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0073</v>
+        <v>0.0057</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>-0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6189</v>
+        <v>3.5932</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0703</v>
+        <v>3.1547</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5487</v>
+        <v>0.4386</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5948</v>
+        <v>1.5831</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3998</v>
+        <v>-0.6218</v>
       </c>
       <c r="I5" t="n">
-        <v>2.195</v>
+        <v>2.2049</v>
       </c>
       <c r="J5" t="n">
-        <v>1.369</v>
+        <v>2.1017</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1176</v>
+        <v>0.1043</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2514</v>
+        <v>1.9974</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2258</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2822</v>
+        <v>-0.7261</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9436</v>
+        <v>0.2075</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2258</v>
+        <v>0.7086</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2987</v>
+        <v>0.0709</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8209</v>
+        <v>2.2317</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0288</v>
+        <v>2.1034</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2078</v>
+        <v>0.1282</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6128</v>
@@ -922,13 +922,13 @@
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3462</v>
+        <v>0.7569</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3031</v>
+        <v>0.3778</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0431</v>
+        <v>0.3791</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0969</v>
+        <v>-0.0626</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7857</v>
+        <v>-1.5498</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6888</v>
+        <v>1.4871</v>
       </c>
       <c r="G7" t="n">
         <v>0.9866</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1485</v>
+        <v>0.1828</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6713</v>
+        <v>0.4696</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>A. RADANOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3766</v>
+        <v>-1.2469</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2503</v>
+        <v>0.4128</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8737</v>
+        <v>-1.6597</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6856</v>
+        <v>0.4778</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8463000000000001</v>
+        <v>1.2172</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1607</v>
+        <v>-0.7395</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.311</v>
+        <v>0.9317</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4214</v>
+        <v>1.0923</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104</v>
+        <v>-0.1607</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6254</v>
+        <v>-0.4539</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5752</v>
+        <v>0.1249</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0502</v>
+        <v>-0.5788</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9843</v>
+        <v>-0.0442</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6122</v>
+        <v>-0.2869</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3721</v>
+        <v>0.2427</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2836</v>
+        <v>-2.1444</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2836</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7444</v>
+        <v>-1.2928</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2058</v>
+        <v>-2.2497</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9502</v>
+        <v>0.9568</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4185</v>
+        <v>-1.3341</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9233</v>
+        <v>0.8475</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3418</v>
+        <v>-2.1817</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0308</v>
+        <v>-1.7309</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6322</v>
+        <v>0.5546</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3986</v>
+        <v>-2.2854</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6123</v>
+        <v>0.3967</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5556</v>
+        <v>0.293</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0568</v>
+        <v>0.1038</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2135</v>
+        <v>-0.1907</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8862</v>
+        <v>-0.2869</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3273</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3271</v>
+        <v>-1.4478</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4856</v>
+        <v>-3.3551</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1585</v>
+        <v>1.9073</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3341</v>
+        <v>-0.6856</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8475</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1817</v>
+        <v>0.1607</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7309</v>
+        <v>-1.311</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5546</v>
+        <v>-1.4214</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2854</v>
+        <v>0.1104</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3967</v>
+        <v>0.6254</v>
       </c>
       <c r="N10" t="n">
-        <v>0.293</v>
+        <v>0.5752</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1038</v>
+        <v>0.0502</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2249</v>
+        <v>0.9131</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>0.5074</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2978</v>
+        <v>0.4057</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RADANOV</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5836</v>
+        <v>-2.8594</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1769</v>
+        <v>-3.7157</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7606</v>
+        <v>0.8563</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4778</v>
+        <v>-4.4236</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2172</v>
+        <v>-0.773</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7395</v>
+        <v>-3.6506</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9317</v>
+        <v>-2.2967</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0923</v>
+        <v>0.4572</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1607</v>
+        <v>-2.754</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4539</v>
+        <v>-2.1269</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1249</v>
+        <v>-1.2303</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5788</v>
+        <v>-0.8966</v>
       </c>
       <c r="P11" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3809</v>
+        <v>0.3117</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5228</v>
+        <v>-0.0272</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1419</v>
+        <v>0.3389</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1055</v>
+        <v>-2.9011</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6593</v>
+        <v>-0.9173</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5538</v>
+        <v>-1.9838</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.4236</v>
+        <v>0.4185</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.773</v>
+        <v>-0.9233</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.6506</v>
+        <v>1.3418</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2967</v>
+        <v>2.0308</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4572</v>
+        <v>0.6322</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.754</v>
+        <v>1.3986</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1269</v>
+        <v>-1.6123</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2303</v>
+        <v>-1.5556</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8966</v>
+        <v>-0.0568</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9344</v>
+        <v>1.0567</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9709</v>
+        <v>0.7631</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0365</v>
+        <v>0.2937</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7886</v>
+        <v>-3.2166</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7886</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.3994</v>
+        <v>12.7731</v>
       </c>
       <c r="E13" t="n">
-        <v>4.031699999999999</v>
+        <v>4.405</v>
       </c>
       <c r="F13" t="n">
-        <v>8.367900000000001</v>
+        <v>8.367799999999997</v>
       </c>
       <c r="G13" t="n">
         <v>6.271500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2155000000000005</v>
+        <v>0.2155000000000007</v>
       </c>
       <c r="I13" t="n">
-        <v>6.055799999999999</v>
+        <v>6.0558</v>
       </c>
       <c r="J13" t="n">
         <v>11.2061</v>
@@ -1447,16 +1447,16 @@
         <v>5.117599999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>6.088400000000004</v>
+        <v>6.088400000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.934699999999999</v>
+        <v>-4.9347</v>
       </c>
       <c r="N13" t="n">
         <v>-4.9021</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.03259999999999985</v>
+        <v>-0.0326</v>
       </c>
       <c r="P13" t="n">
         <v>5.7988</v>
@@ -1468,16 +1468,16 @@
         <v>18.5563</v>
       </c>
       <c r="S13" t="n">
-        <v>3.971299999999999</v>
+        <v>4.3446</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4741999999999992</v>
+        <v>0.8477000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>3.496900000000001</v>
+        <v>3.4968</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.642</v>
+        <v>-3.642000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.108499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3998</v>
+        <v>2.8601</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4222</v>
+        <v>1.7145</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9776</v>
+        <v>1.1457</v>
       </c>
       <c r="G14" t="n">
         <v>0.1223</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0635</v>
+        <v>0.5239</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0499</v>
+        <v>0.3422</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0136</v>
+        <v>0.1817</v>
       </c>
       <c r="V14" t="n">
         <v>1.7501</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7551</v>
+        <v>1.116</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3751</v>
+        <v>-0.611</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1302</v>
+        <v>1.727</v>
       </c>
       <c r="G15" t="n">
         <v>1.37</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9419</v>
+        <v>0.3027</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1889</v>
+        <v>-0.047</v>
       </c>
       <c r="U15" t="n">
-        <v>0.753</v>
+        <v>0.3497</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7886</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8452</v>
+        <v>0.7114</v>
       </c>
       <c r="E16" t="n">
-        <v>0.587</v>
+        <v>0.8229</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2582</v>
+        <v>-0.1115</v>
       </c>
       <c r="G16" t="n">
         <v>0.6186</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3844</v>
+        <v>-0.5181</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>-0.3536</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2052</v>
+        <v>-0.1645</v>
       </c>
       <c r="V16" t="n">
         <v>2.0026</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2029</v>
+        <v>-0.5871</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2652</v>
+        <v>-0.5241</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0623</v>
+        <v>-0.0631</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2921</v>
+        <v>0.9552</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4357</v>
+        <v>-1.6447</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8564000000000001</v>
+        <v>2.5998</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3103</v>
+        <v>1.1948</v>
       </c>
       <c r="K17" t="n">
-        <v>1.163</v>
+        <v>-1.5153</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1472</v>
+        <v>2.7101</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6023</v>
+        <v>-0.2397</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5987</v>
+        <v>-0.1294</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0037</v>
+        <v>-0.1103</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5825</v>
+        <v>-0.7589</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1019</v>
+        <v>-0.2396</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6844</v>
+        <v>-0.5192</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5021</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1702</v>
+        <v>-0.0887</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3319</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9552</v>
+        <v>-1.2921</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6447</v>
+        <v>-0.4357</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5998</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1948</v>
+        <v>1.3103</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5153</v>
+        <v>1.163</v>
       </c>
       <c r="L18" t="n">
-        <v>2.7101</v>
+        <v>0.1472</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2397</v>
+        <v>-2.6023</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1294</v>
+        <v>-1.5987</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1103</v>
+        <v>-1.0037</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.2418</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1142</v>
+        <v>-0.4558</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7881</v>
+        <v>0.2139</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6152</v>
+        <v>-0.6989</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6911</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0759</v>
+        <v>-0.1257</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7637</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0835</v>
+        <v>-0.1672</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1406</v>
+        <v>-0.0611</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8036</v>
+        <v>-2.7528</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7164</v>
+        <v>-1.5985</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0871</v>
+        <v>-1.1544</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1836</v>
@@ -2014,13 +2014,13 @@
         <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2283</v>
+        <v>-1.1775</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.963</v>
+        <v>-0.845</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2653</v>
+        <v>-0.3325</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2797</v>
+        <v>-3.489</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3375</v>
+        <v>-3.9836</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0577</v>
+        <v>0.4946</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2544</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.01</v>
+        <v>-0.2192</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6721</v>
+        <v>-0.3183</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3378</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>1.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6873</v>
+        <v>-4.2497</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.235</v>
+        <v>-0.9991</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4522</v>
+        <v>-3.2506</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1362</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8705</v>
+        <v>-1.433</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0376</v>
+        <v>-0.8017</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8329</v>
+        <v>-0.6313</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7146</v>
+        <v>-4.688</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1169</v>
+        <v>-2.5271</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5977</v>
+        <v>-2.1608</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7075</v>
@@ -2248,13 +2248,13 @@
         <v>2.3195</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3087</v>
+        <v>-0.282</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2617</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.047</v>
+        <v>0.3899</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5387</v>
@@ -2284,7 +2284,7 @@
         <v>-12.3995</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.367800000000001</v>
+        <v>-8.367800000000003</v>
       </c>
       <c r="F24" t="n">
         <v>-4.0316</v>
@@ -2326,13 +2326,13 @@
         <v>12.7575</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.9714</v>
+        <v>-3.9711</v>
       </c>
       <c r="T24" t="n">
         <v>-3.4968</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4743</v>
+        <v>-0.4742999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>3.642000000000001</v>
